--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_PARIS BASKETBALL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_PARIS BASKETBALL.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>27.3035</v>
+        <v>35.7894</v>
       </c>
       <c r="E2" t="n">
-        <v>19.233</v>
+        <v>32.8272</v>
       </c>
       <c r="F2" t="n">
-        <v>8.0708</v>
+        <v>2.9619</v>
       </c>
       <c r="G2" t="n">
-        <v>1.489700000000001</v>
+        <v>27.9499</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07079999999999975</v>
+        <v>3.053700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4191</v>
+        <v>24.8967</v>
       </c>
       <c r="J2" t="n">
-        <v>16.2998</v>
+        <v>58.3236</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4044</v>
+        <v>17.2302</v>
       </c>
       <c r="L2" t="n">
-        <v>10.8951</v>
+        <v>41.0938</v>
       </c>
       <c r="M2" t="n">
-        <v>-14.8097</v>
+        <v>-30.3732</v>
       </c>
       <c r="N2" t="n">
-        <v>-5.334000000000001</v>
+        <v>-14.1766</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.476099999999999</v>
+        <v>-16.197</v>
       </c>
       <c r="P2" t="n">
-        <v>21.3401</v>
+        <v>-25.0513</v>
       </c>
       <c r="Q2" t="n">
-        <v>-17.8608</v>
+        <v>-87.4462</v>
       </c>
       <c r="R2" t="n">
-        <v>39.2002</v>
+        <v>62.3957</v>
       </c>
       <c r="S2" t="n">
-        <v>11.2531</v>
+        <v>-6.4006</v>
       </c>
       <c r="T2" t="n">
-        <v>9.7569</v>
+        <v>-1.6696</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4964</v>
+        <v>-4.7306</v>
       </c>
       <c r="V2" t="n">
-        <v>-6.779</v>
+        <v>39.2906</v>
       </c>
       <c r="W2" t="n">
-        <v>11.0367</v>
+        <v>63.6191</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.8157</v>
+        <v>-24.3285</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>26.293</v>
+        <v>34.0825</v>
       </c>
       <c r="E3" t="n">
-        <v>36.3739</v>
+        <v>29.6822</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.081</v>
+        <v>4.4003</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9956</v>
+        <v>16.4842</v>
       </c>
       <c r="H3" t="n">
-        <v>9.7141</v>
+        <v>-12.6102</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.7187</v>
+        <v>29.0946</v>
       </c>
       <c r="J3" t="n">
-        <v>31.3792</v>
+        <v>52.1146</v>
       </c>
       <c r="K3" t="n">
-        <v>19.9693</v>
+        <v>2.862100000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>11.4088</v>
+        <v>49.2526</v>
       </c>
       <c r="M3" t="n">
-        <v>-28.3832</v>
+        <v>-35.6301</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.2555</v>
+        <v>-15.472</v>
       </c>
       <c r="O3" t="n">
-        <v>-18.1278</v>
+        <v>-20.1582</v>
       </c>
       <c r="P3" t="n">
-        <v>8.582199999999998</v>
+        <v>-38.5041</v>
       </c>
       <c r="Q3" t="n">
-        <v>-39.664</v>
+        <v>-103.9144</v>
       </c>
       <c r="R3" t="n">
-        <v>48.2465</v>
+        <v>65.4109</v>
       </c>
       <c r="S3" t="n">
-        <v>44.5462</v>
+        <v>-4.5221</v>
       </c>
       <c r="T3" t="n">
-        <v>41.5086</v>
+        <v>0.1406000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>3.038</v>
+        <v>-4.6622</v>
       </c>
       <c r="V3" t="n">
-        <v>-29.8313</v>
+        <v>60.6238</v>
       </c>
       <c r="W3" t="n">
-        <v>3.150500000000001</v>
+        <v>81.34139999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-32.9819</v>
+        <v>-20.7176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>23.9305</v>
+        <v>22.8217</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8109</v>
+        <v>15.9769</v>
       </c>
       <c r="F4" t="n">
-        <v>22.1194</v>
+        <v>6.8447</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.787200000000001</v>
+        <v>1.489700000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.577199999999999</v>
+        <v>0.07079999999999975</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7898</v>
+        <v>1.4191</v>
       </c>
       <c r="J4" t="n">
-        <v>11.1823</v>
+        <v>16.2998</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9059</v>
+        <v>5.4044</v>
       </c>
       <c r="L4" t="n">
-        <v>7.2762</v>
+        <v>10.8951</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.9696</v>
+        <v>-14.8097</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.4834</v>
+        <v>-5.334000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4861</v>
+        <v>-9.476099999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>27.6025</v>
+        <v>21.3401</v>
       </c>
       <c r="Q4" t="n">
-        <v>-20.8762</v>
+        <v>-17.8608</v>
       </c>
       <c r="R4" t="n">
-        <v>48.4784</v>
+        <v>39.2002</v>
       </c>
       <c r="S4" t="n">
-        <v>13.2195</v>
+        <v>6.7711</v>
       </c>
       <c r="T4" t="n">
-        <v>9.439500000000001</v>
+        <v>6.5008</v>
       </c>
       <c r="U4" t="n">
-        <v>3.7799</v>
+        <v>0.2706000000000002</v>
       </c>
       <c r="V4" t="n">
-        <v>-15.1041</v>
+        <v>-6.779</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0648</v>
+        <v>11.0367</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.1689</v>
+        <v>-17.8157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>23.877</v>
+        <v>16.9209</v>
       </c>
       <c r="E5" t="n">
-        <v>10.1207</v>
+        <v>-4.307100000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>13.7565</v>
+        <v>21.2281</v>
       </c>
       <c r="G5" t="n">
-        <v>27.2181</v>
+        <v>-1.787200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>13.701</v>
+        <v>-6.577199999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>13.5176</v>
+        <v>4.7898</v>
       </c>
       <c r="J5" t="n">
-        <v>50.3448</v>
+        <v>11.1823</v>
       </c>
       <c r="K5" t="n">
-        <v>27.9674</v>
+        <v>3.9059</v>
       </c>
       <c r="L5" t="n">
-        <v>22.377</v>
+        <v>7.2762</v>
       </c>
       <c r="M5" t="n">
-        <v>-23.1269</v>
+        <v>-12.9696</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.2666</v>
+        <v>-10.4834</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.860199999999999</v>
+        <v>-2.4861</v>
       </c>
       <c r="P5" t="n">
-        <v>-19.7159</v>
+        <v>27.6025</v>
       </c>
       <c r="Q5" t="n">
-        <v>-71.6735</v>
+        <v>-20.8762</v>
       </c>
       <c r="R5" t="n">
-        <v>51.9578</v>
+        <v>48.4784</v>
       </c>
       <c r="S5" t="n">
-        <v>44.6949</v>
+        <v>6.2099</v>
       </c>
       <c r="T5" t="n">
-        <v>32.051</v>
+        <v>3.3217</v>
       </c>
       <c r="U5" t="n">
-        <v>12.644</v>
+        <v>2.8888</v>
       </c>
       <c r="V5" t="n">
-        <v>-28.3202</v>
+        <v>-15.1041</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6021999999999996</v>
+        <v>2.0648</v>
       </c>
       <c r="X5" t="n">
-        <v>-27.718</v>
+        <v>-17.1689</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>10.4889</v>
+        <v>15.5968</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3867</v>
+        <v>12.3593</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.8975</v>
+        <v>3.2375</v>
       </c>
       <c r="G6" t="n">
-        <v>27.9499</v>
+        <v>8.976599999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.053700000000001</v>
+        <v>-2.7936</v>
       </c>
       <c r="I6" t="n">
-        <v>24.8967</v>
+        <v>11.771</v>
       </c>
       <c r="J6" t="n">
-        <v>58.3236</v>
+        <v>33.7494</v>
       </c>
       <c r="K6" t="n">
-        <v>17.2302</v>
+        <v>5.2423</v>
       </c>
       <c r="L6" t="n">
-        <v>41.0938</v>
+        <v>28.5071</v>
       </c>
       <c r="M6" t="n">
-        <v>-30.3732</v>
+        <v>-24.7725</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.1766</v>
+        <v>-8.036</v>
       </c>
       <c r="O6" t="n">
-        <v>-16.197</v>
+        <v>-16.7367</v>
       </c>
       <c r="P6" t="n">
-        <v>-25.0513</v>
+        <v>19.0204</v>
       </c>
       <c r="Q6" t="n">
-        <v>-87.4462</v>
+        <v>-31.082</v>
       </c>
       <c r="R6" t="n">
-        <v>62.3957</v>
+        <v>50.1018</v>
       </c>
       <c r="S6" t="n">
-        <v>-31.7011</v>
+        <v>1.9154</v>
       </c>
       <c r="T6" t="n">
-        <v>-19.1106</v>
+        <v>4.9772</v>
       </c>
       <c r="U6" t="n">
-        <v>-12.5907</v>
+        <v>-3.0618</v>
       </c>
       <c r="V6" t="n">
-        <v>39.2906</v>
+        <v>-14.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>63.6191</v>
+        <v>4.7142</v>
       </c>
       <c r="X6" t="n">
-        <v>-24.3285</v>
+        <v>-19.0297</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>7.2184</v>
+        <v>2.2111</v>
       </c>
       <c r="E7" t="n">
-        <v>9.1197</v>
+        <v>-3.794200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9017</v>
+        <v>6.005300000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>8.976599999999999</v>
+        <v>-6.3024</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7936</v>
+        <v>-4.994200000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>11.771</v>
+        <v>-1.307799999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>33.7494</v>
+        <v>11.1348</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2423</v>
+        <v>7.5146</v>
       </c>
       <c r="L7" t="n">
-        <v>28.5071</v>
+        <v>3.6208</v>
       </c>
       <c r="M7" t="n">
-        <v>-24.7725</v>
+        <v>-17.437</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.036</v>
+        <v>-12.5085</v>
       </c>
       <c r="O7" t="n">
-        <v>-16.7367</v>
+        <v>-4.928299999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>19.0204</v>
+        <v>28.0665</v>
       </c>
       <c r="Q7" t="n">
-        <v>-31.082</v>
+        <v>-25.747</v>
       </c>
       <c r="R7" t="n">
-        <v>50.1018</v>
+        <v>53.8132</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.4633</v>
+        <v>-3.4082</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7377</v>
+        <v>-1.9385</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.2005</v>
+        <v>-1.4697</v>
       </c>
       <c r="V7" t="n">
-        <v>-14.3155</v>
+        <v>-16.1452</v>
       </c>
       <c r="W7" t="n">
-        <v>4.7142</v>
+        <v>12.7557</v>
       </c>
       <c r="X7" t="n">
-        <v>-19.0297</v>
+        <v>-28.9009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>5.623100000000001</v>
+        <v>-3.218500000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>7.1348</v>
+        <v>10.3849</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.511300000000001</v>
+        <v>-13.603</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4842</v>
+        <v>2.9956</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.6102</v>
+        <v>9.7141</v>
       </c>
       <c r="I8" t="n">
-        <v>29.0946</v>
+        <v>-6.7187</v>
       </c>
       <c r="J8" t="n">
-        <v>52.1146</v>
+        <v>31.3792</v>
       </c>
       <c r="K8" t="n">
-        <v>2.862100000000001</v>
+        <v>19.9693</v>
       </c>
       <c r="L8" t="n">
-        <v>49.2526</v>
+        <v>11.4088</v>
       </c>
       <c r="M8" t="n">
-        <v>-35.6301</v>
+        <v>-28.3832</v>
       </c>
       <c r="N8" t="n">
-        <v>-15.472</v>
+        <v>-10.2555</v>
       </c>
       <c r="O8" t="n">
-        <v>-20.1582</v>
+        <v>-18.1278</v>
       </c>
       <c r="P8" t="n">
-        <v>-38.5041</v>
+        <v>8.582199999999998</v>
       </c>
       <c r="Q8" t="n">
-        <v>-103.9144</v>
+        <v>-39.664</v>
       </c>
       <c r="R8" t="n">
-        <v>65.4109</v>
+        <v>48.2465</v>
       </c>
       <c r="S8" t="n">
-        <v>-32.9814</v>
+        <v>15.035</v>
       </c>
       <c r="T8" t="n">
-        <v>-22.4077</v>
+        <v>15.5192</v>
       </c>
       <c r="U8" t="n">
-        <v>-10.5741</v>
+        <v>-0.4841999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>60.6238</v>
+        <v>-29.8313</v>
       </c>
       <c r="W8" t="n">
-        <v>81.34139999999999</v>
+        <v>3.150500000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.7176</v>
+        <v>-32.9819</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. SHAHRVIN</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.023</v>
+        <v>-4.0418</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5801</v>
+        <v>-11.0954</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5571</v>
+        <v>7.0539</v>
       </c>
       <c r="G9" t="n">
-        <v>1.420200000000001</v>
+        <v>27.2181</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4774999999999998</v>
+        <v>13.701</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8977</v>
+        <v>13.5176</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5086</v>
+        <v>50.3448</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7482</v>
+        <v>27.9674</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7603</v>
+        <v>22.377</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0886</v>
+        <v>-23.1269</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2259</v>
+        <v>-14.2666</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8626999999999999</v>
+        <v>-8.860199999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>-19.7159</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.1183</v>
+        <v>-71.6735</v>
       </c>
       <c r="R9" t="n">
-        <v>9.046299999999999</v>
+        <v>51.9578</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2763</v>
+        <v>16.7762</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2124</v>
+        <v>10.8352</v>
       </c>
       <c r="U9" t="n">
-        <v>2.0638</v>
+        <v>5.940799999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.6472</v>
+        <v>-28.3202</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.1829</v>
+        <v>-0.6021999999999996</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.4643</v>
+        <v>-27.718</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>E. SHAHRVIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.162500000000001</v>
+        <v>-4.898300000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8449</v>
+        <v>-5.1567</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3175</v>
+        <v>0.2586999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4772</v>
+        <v>1.420200000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4014</v>
+        <v>-0.4774999999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.878500000000001</v>
+        <v>1.8977</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4164999999999996</v>
+        <v>4.5086</v>
       </c>
       <c r="K10" t="n">
-        <v>3.382</v>
+        <v>1.7482</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.7986</v>
+        <v>2.7603</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0604</v>
+        <v>-3.0886</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9803</v>
+        <v>-2.2259</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0798</v>
+        <v>-0.8626999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>2.319499999999999</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.9019</v>
+        <v>-8.1183</v>
       </c>
       <c r="R10" t="n">
-        <v>13.2214</v>
+        <v>9.046299999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>5.0704</v>
+        <v>0.401</v>
       </c>
       <c r="T10" t="n">
-        <v>6.4738</v>
+        <v>-0.3641</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4031</v>
+        <v>0.7651999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.0752</v>
+        <v>-7.6472</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.0752</v>
+        <v>-6.4643</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.546</v>
+        <v>-7.0496</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2629</v>
+        <v>-3.0137</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.282999999999999</v>
+        <v>-4.0359</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4116</v>
@@ -1312,13 +1312,13 @@
         <v>7.422599999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3062</v>
+        <v>1.8027</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8713</v>
+        <v>2.1203</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5648000000000001</v>
+        <v>-0.3176</v>
       </c>
       <c r="V11" t="n">
         <v>-5.9768</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.0783</v>
+        <v>-8.394</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5513</v>
+        <v>-6.830499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.6296</v>
+        <v>-1.5636</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4101000000000008</v>
+        <v>-3.4772</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7174000000000003</v>
+        <v>1.4014</v>
       </c>
       <c r="I12" t="n">
-        <v>1.127299999999999</v>
+        <v>-4.878500000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>15.2137</v>
+        <v>-0.4164999999999996</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4139</v>
+        <v>3.382</v>
       </c>
       <c r="L12" t="n">
-        <v>12.7998</v>
+        <v>-3.7986</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.804</v>
+        <v>-3.0604</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.1316</v>
+        <v>-1.9803</v>
       </c>
       <c r="O12" t="n">
-        <v>-11.6724</v>
+        <v>-1.0798</v>
       </c>
       <c r="P12" t="n">
-        <v>8.118499999999999</v>
+        <v>2.319499999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.541</v>
+        <v>-10.9019</v>
       </c>
       <c r="R12" t="n">
-        <v>23.6594</v>
+        <v>13.2214</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2039</v>
+        <v>2.8387</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7279</v>
+        <v>4.4878</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4759000000000002</v>
+        <v>-1.6493</v>
       </c>
       <c r="V12" t="n">
-        <v>-20.4029</v>
+        <v>-10.0752</v>
       </c>
       <c r="W12" t="n">
-        <v>6.606100000000001</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-27.009</v>
+        <v>-10.0752</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.1294</v>
+        <v>-11.6624</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.3756</v>
+        <v>6.26</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7538</v>
+        <v>-17.9227</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.3024</v>
+        <v>0.4101000000000008</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.994200000000001</v>
+        <v>-0.7174000000000003</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.307799999999999</v>
+        <v>1.127299999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>11.1348</v>
+        <v>15.2137</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5146</v>
+        <v>2.4139</v>
       </c>
       <c r="L13" t="n">
-        <v>3.6208</v>
+        <v>12.7998</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.437</v>
+        <v>-14.804</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.5085</v>
+        <v>-3.1316</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.928299999999999</v>
+        <v>-11.6724</v>
       </c>
       <c r="P13" t="n">
-        <v>28.0665</v>
+        <v>8.118499999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-25.747</v>
+        <v>-15.541</v>
       </c>
       <c r="R13" t="n">
-        <v>53.8132</v>
+        <v>23.6594</v>
       </c>
       <c r="S13" t="n">
-        <v>-20.7482</v>
+        <v>0.212</v>
       </c>
       <c r="T13" t="n">
-        <v>-11.5197</v>
+        <v>-0.01919999999999988</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.2285</v>
+        <v>0.2315999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-16.1452</v>
+        <v>-20.4029</v>
       </c>
       <c r="W13" t="n">
-        <v>12.7557</v>
+        <v>6.606100000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-28.9009</v>
+        <v>-27.009</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.7278</v>
+        <v>-17.2033</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.7904</v>
+        <v>-18.4617</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.9373</v>
+        <v>1.2581</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.7462</v>
+        <v>-32.3583</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.6952</v>
+        <v>-30.2201</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.051</v>
+        <v>-2.1379</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2491</v>
+        <v>1.311199999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.6924</v>
+        <v>-15.8199</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9417</v>
+        <v>17.131</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.9954</v>
+        <v>-33.6699</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.003</v>
+        <v>-14.4002</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.9925</v>
+        <v>-19.2691</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4794</v>
+        <v>14.6133</v>
       </c>
       <c r="Q14" t="n">
-        <v>-29.4583</v>
+        <v>-34.0973</v>
       </c>
       <c r="R14" t="n">
-        <v>32.9375</v>
+        <v>48.7105</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.6021</v>
+        <v>1.3619</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.474400000000001</v>
+        <v>5.8258</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.1279</v>
+        <v>-4.4642</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.8586</v>
+        <v>-0.8197000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>15.8927</v>
+        <v>8.498000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.7513</v>
+        <v>-9.3177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>-29.9621</v>
+        <v>-19.442</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.2866</v>
+        <v>-1.5396</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.675</v>
+        <v>-17.9021</v>
       </c>
       <c r="G15" t="n">
-        <v>-32.3583</v>
+        <v>-21.848</v>
       </c>
       <c r="H15" t="n">
-        <v>-30.2201</v>
+        <v>-5.6064</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1379</v>
+        <v>-16.2416</v>
       </c>
       <c r="J15" t="n">
-        <v>1.311199999999998</v>
+        <v>13.5887</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.8199</v>
+        <v>9.416399999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>17.131</v>
+        <v>4.1721</v>
       </c>
       <c r="M15" t="n">
-        <v>-33.6699</v>
+        <v>-35.4368</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.4002</v>
+        <v>-15.0229</v>
       </c>
       <c r="O15" t="n">
-        <v>-19.2691</v>
+        <v>-20.4139</v>
       </c>
       <c r="P15" t="n">
-        <v>14.6133</v>
+        <v>3.0154</v>
       </c>
       <c r="Q15" t="n">
-        <v>-34.0973</v>
+        <v>-43.8395</v>
       </c>
       <c r="R15" t="n">
-        <v>48.7105</v>
+        <v>46.8548</v>
       </c>
       <c r="S15" t="n">
-        <v>-11.3969</v>
+        <v>-3.2895</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9993</v>
+        <v>4.744899999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-10.3979</v>
+        <v>-8.0344</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8197000000000001</v>
+        <v>2.680499999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>8.498000000000001</v>
+        <v>23.9653</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.3177</v>
+        <v>-21.2848</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-34.8824</v>
+        <v>-24.1427</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.1849</v>
+        <v>-10.2966</v>
       </c>
       <c r="F16" t="n">
-        <v>-24.6969</v>
+        <v>-13.8459</v>
       </c>
       <c r="G16" t="n">
-        <v>-21.848</v>
+        <v>-16.7462</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.6064</v>
+        <v>-12.6952</v>
       </c>
       <c r="I16" t="n">
-        <v>-16.2416</v>
+        <v>-4.051</v>
       </c>
       <c r="J16" t="n">
-        <v>13.5887</v>
+        <v>4.2491</v>
       </c>
       <c r="K16" t="n">
-        <v>9.416399999999999</v>
+        <v>-3.6924</v>
       </c>
       <c r="L16" t="n">
-        <v>4.1721</v>
+        <v>7.9417</v>
       </c>
       <c r="M16" t="n">
-        <v>-35.4368</v>
+        <v>-20.9954</v>
       </c>
       <c r="N16" t="n">
-        <v>-15.0229</v>
+        <v>-9.003</v>
       </c>
       <c r="O16" t="n">
-        <v>-20.4139</v>
+        <v>-11.9925</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0154</v>
+        <v>3.4794</v>
       </c>
       <c r="Q16" t="n">
-        <v>-43.8395</v>
+        <v>-29.4583</v>
       </c>
       <c r="R16" t="n">
-        <v>46.8548</v>
+        <v>32.9375</v>
       </c>
       <c r="S16" t="n">
-        <v>-18.7297</v>
+        <v>-4.0172</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.9002</v>
+        <v>-0.9806</v>
       </c>
       <c r="U16" t="n">
-        <v>-14.8297</v>
+        <v>-3.0365</v>
       </c>
       <c r="V16" t="n">
-        <v>2.680499999999999</v>
+        <v>-6.8586</v>
       </c>
       <c r="W16" t="n">
-        <v>23.9653</v>
+        <v>15.8927</v>
       </c>
       <c r="X16" t="n">
-        <v>-21.2848</v>
+        <v>-22.7513</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-38.71</v>
+        <v>-29.5604</v>
       </c>
       <c r="E17" t="n">
-        <v>-35.9114</v>
+        <v>-29.0863</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7984</v>
+        <v>-0.4747999999999994</v>
       </c>
       <c r="G17" t="n">
         <v>-13.4875</v>
@@ -1780,13 +1780,13 @@
         <v>45.6951</v>
       </c>
       <c r="S17" t="n">
-        <v>-9.9498</v>
+        <v>-0.8004000000000004</v>
       </c>
       <c r="T17" t="n">
-        <v>-5.653799999999999</v>
+        <v>1.1712</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.2954</v>
+        <v>-1.9716</v>
       </c>
       <c r="V17" t="n">
         <v>-1.355799999999999</v>
@@ -1813,25 +1813,25 @@
         <v>38</v>
       </c>
       <c r="D18" t="n">
-        <v>-50.48710000000001</v>
+        <v>-2.190600000000003</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.505800000000001</v>
+        <v>13.90869999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-45.97920000000001</v>
+        <v>-16.0995</v>
       </c>
       <c r="G18" t="n">
         <v>-11.47399999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-62.32690000000001</v>
+        <v>-62.3269</v>
       </c>
       <c r="I18" t="n">
-        <v>50.8557</v>
+        <v>50.85570000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>319.5287999999999</v>
+        <v>319.5288</v>
       </c>
       <c r="K18" t="n">
         <v>88.9739</v>
@@ -1858,16 +1858,16 @@
         <v>647.1521</v>
       </c>
       <c r="S18" t="n">
-        <v>-17.4098</v>
+        <v>30.8859</v>
       </c>
       <c r="T18" t="n">
-        <v>36.2576</v>
+        <v>54.67270000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-53.6664</v>
+        <v>-23.7851</v>
       </c>
       <c r="V18" t="n">
-        <v>-61.03659999999998</v>
+        <v>-61.03659999999999</v>
       </c>
       <c r="W18" t="n">
         <v>247.4199</v>
